--- a/hddt-SES/src/main/resources/static/cttncn/MauUploadCT_TNCN-TT78.xlsx
+++ b/hddt-SES/src/main/resources/static/cttncn/MauUploadCT_TNCN-TT78.xlsx
@@ -1,44 +1,45 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26227"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VAN HAU\Desktop\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7723AB6C-BA93-45DF-8F51-2D93E3683990}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{1AF43CFE-FB0D-429C-9C56-4134A49B1F97}"/>
+    <workbookView windowWidth="28800" windowHeight="11730"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>VAN HAU</author>
     <author>ASIA</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{BD656075-F7BA-4535-A535-6DB547057AA1}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
+    <comment ref="A1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
             <rFont val="Tahoma"/>
             <charset val="1"/>
           </rPr>
@@ -47,7 +48,6 @@
         <r>
           <rPr>
             <sz val="9"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <charset val="1"/>
           </rPr>
@@ -56,13 +56,12 @@
         </r>
       </text>
     </comment>
-    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{C1755CD9-C22D-42CF-A426-7CBD40D74611}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
+    <comment ref="B1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
             <rFont val="Tahoma"/>
             <charset val="1"/>
           </rPr>
@@ -71,7 +70,6 @@
         <r>
           <rPr>
             <sz val="9"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <charset val="1"/>
           </rPr>
@@ -80,13 +78,12 @@
         </r>
       </text>
     </comment>
-    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{7CAFE004-B3FB-4C76-B095-C9A014EC1863}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
+    <comment ref="C1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
             <rFont val="Tahoma"/>
             <charset val="1"/>
           </rPr>
@@ -94,13 +91,12 @@
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{F84F9824-BDDC-4B7A-A8A4-7DC82DE1E82D}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
+    <comment ref="D1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
             <rFont val="Tahoma"/>
             <charset val="1"/>
           </rPr>
@@ -108,13 +104,12 @@
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{8DFA1725-728E-48FF-8251-17703FFE8699}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
+    <comment ref="E1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
             <rFont val="Tahoma"/>
             <charset val="1"/>
           </rPr>
@@ -122,13 +117,12 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{A3BF9FE8-5E5B-44A2-A649-5D6D7898E702}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
+    <comment ref="F1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
             <rFont val="Tahoma"/>
             <charset val="1"/>
           </rPr>
@@ -136,13 +130,12 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{EB904E0B-DDAE-4522-9380-8D865A8B9757}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
+    <comment ref="G1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
             <rFont val="Tahoma"/>
             <charset val="1"/>
           </rPr>
@@ -150,13 +143,12 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{D12332DE-E0F8-40BF-BAFE-453D62990EEA}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
+    <comment ref="H1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
             <rFont val="Tahoma"/>
             <charset val="1"/>
           </rPr>
@@ -164,13 +156,12 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{5064A13F-F607-47EF-BB47-1E6E5AC77EE6}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
+    <comment ref="I1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
             <rFont val="Tahoma"/>
             <charset val="1"/>
           </rPr>
@@ -178,13 +169,12 @@
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="1" shapeId="0" xr:uid="{27CB0DBE-9DF0-43A7-B197-5835C8BD2711}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
+    <comment ref="J1" authorId="1">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
             <rFont val="Tahoma"/>
             <charset val="1"/>
           </rPr>
@@ -194,13 +184,12 @@
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{FE00B716-B50D-4FEB-899D-FAA3E97A8A07}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
+    <comment ref="K1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
             <rFont val="Tahoma"/>
             <charset val="1"/>
           </rPr>
@@ -208,13 +197,12 @@
         </r>
       </text>
     </comment>
-    <comment ref="L1" authorId="0" shapeId="0" xr:uid="{F7D8051F-0CE0-4D5A-BB59-8AA9B435B600}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
+    <comment ref="L1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
             <rFont val="Tahoma"/>
             <charset val="1"/>
           </rPr>
@@ -222,51 +210,38 @@
         </r>
       </text>
     </comment>
-    <comment ref="M1" authorId="1" shapeId="0" xr:uid="{EEB5EE67-509D-4CAC-9171-CC635056113A}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
+    <comment ref="M1" authorId="1">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="Tahoma"/>
+            <charset val="134"/>
           </rPr>
           <t>Đến ngày</t>
         </r>
       </text>
     </comment>
-    <comment ref="N1" authorId="1" shapeId="0" xr:uid="{5FD23B0F-DE17-469D-855E-69FF88064F64}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Khoản thu nhập</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="O1" authorId="0" shapeId="0" xr:uid="{F20B80DD-1149-4B8D-9A07-8BD1BF2374BE}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
+    <comment ref="N1" authorId="1">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="Tahoma"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Số tiền đóng BHXH hoặc các loại bảo hiểm bắt buộc tương tự mà đơn vị đã nộp cho nhân viên (khoản trừ trên lương của nhân viên)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="O1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
             <rFont val="Tahoma"/>
             <charset val="1"/>
           </rPr>
@@ -274,13 +249,12 @@
         </r>
       </text>
     </comment>
-    <comment ref="P1" authorId="0" shapeId="0" xr:uid="{D297FFA2-5E05-4B88-B306-2C6DBF5913DF}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
+    <comment ref="P1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
             <rFont val="Tahoma"/>
             <charset val="1"/>
           </rPr>
@@ -288,13 +262,12 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q1" authorId="0" shapeId="0" xr:uid="{6F47B024-48EB-4F15-9C6B-A19DCFD47C01}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
+    <comment ref="Q1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
             <rFont val="Tahoma"/>
             <charset val="1"/>
           </rPr>
@@ -302,15 +275,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="R1" authorId="1" shapeId="0" xr:uid="{E5DE7EF0-1789-472A-B990-086017A5115D}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
+    <comment ref="R1" authorId="1">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="Tahoma"/>
+            <charset val="134"/>
           </rPr>
           <t>Số thuế thu nhập cá nhân đã khấu trừ</t>
         </r>
@@ -323,88 +295,109 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="38">
   <si>
+    <t>MaCT(*)</t>
+  </si>
+  <si>
+    <t>MaSoThue NV</t>
+  </si>
+  <si>
+    <t>TenNV(*)</t>
+  </si>
+  <si>
+    <t>MaNV</t>
+  </si>
+  <si>
+    <t>DiaChiNV</t>
+  </si>
+  <si>
+    <t>CMND-CCCD(*)</t>
+  </si>
+  <si>
+    <t>NgayCap(*)</t>
+  </si>
+  <si>
+    <t>NoiCap(*)</t>
+  </si>
+  <si>
+    <t>QuocTich(*)</t>
+  </si>
+  <si>
+    <t>CaNhanCuTru(*)</t>
+  </si>
+  <si>
+    <t>KyBaoCao(*)</t>
+  </si>
+  <si>
+    <t>TuNgay</t>
+  </si>
+  <si>
+    <t>DenNgay</t>
+  </si>
+  <si>
+    <t>KhoanThuNhap(*)</t>
+  </si>
+  <si>
+    <t>KhoanDongBHBB</t>
+  </si>
+  <si>
+    <t>TongTNChiuThuePhaiKT(*)</t>
+  </si>
+  <si>
+    <t>TongThuNhapTinhThue(*)</t>
+  </si>
+  <si>
+    <t>SoThueTNCN Da KT(*)</t>
+  </si>
+  <si>
     <t>1</t>
   </si>
   <si>
     <t>0107521365</t>
   </si>
   <si>
+    <t>Nguyễn Văn A</t>
+  </si>
+  <si>
+    <t>NV01</t>
+  </si>
+  <si>
+    <t>Địa chỉ A</t>
+  </si>
+  <si>
+    <t>xxxxxxxxx</t>
+  </si>
+  <si>
+    <t>30/03/2023</t>
+  </si>
+  <si>
+    <t>Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>Việt Nam</t>
+  </si>
+  <si>
+    <t>10/03/2023</t>
+  </si>
+  <si>
+    <t>01/04/2023</t>
+  </si>
+  <si>
+    <t>Tiền lương tiền công</t>
+  </si>
+  <si>
     <t>2</t>
   </si>
   <si>
-    <t>Địa chỉ A</t>
-  </si>
-  <si>
-    <t>MaCT(*)</t>
-  </si>
-  <si>
-    <t>MaSoThue NV</t>
-  </si>
-  <si>
-    <t>MaNV</t>
-  </si>
-  <si>
-    <t>DiaChiNV</t>
-  </si>
-  <si>
-    <t>CMND-CCCD(*)</t>
-  </si>
-  <si>
-    <t>TenNV(*)</t>
-  </si>
-  <si>
-    <t>NgayCap(*)</t>
-  </si>
-  <si>
-    <t>NoiCap(*)</t>
-  </si>
-  <si>
-    <t>QuocTich(*)</t>
-  </si>
-  <si>
-    <t>CaNhanCuTru(*)</t>
-  </si>
-  <si>
-    <t>KyBaoCao(*)</t>
-  </si>
-  <si>
-    <t>KhoanThuNhap(*)</t>
-  </si>
-  <si>
-    <t>KhoanDongBHBB</t>
-  </si>
-  <si>
-    <t>TongTNChiuThuePhaiKT(*)</t>
-  </si>
-  <si>
-    <t>TongThuNhapTinhThue(*)</t>
-  </si>
-  <si>
-    <t>SoThueTNCN Da KT(*)</t>
-  </si>
-  <si>
-    <t>Nguyễn Văn A</t>
-  </si>
-  <si>
-    <t>NV01</t>
-  </si>
-  <si>
-    <t>xxxxxxxxx</t>
-  </si>
-  <si>
-    <t>30/03/2023</t>
-  </si>
-  <si>
-    <t>Hồ Chí Minh</t>
-  </si>
-  <si>
-    <t>Việt Nam</t>
-  </si>
-  <si>
-    <t>10/03/2023</t>
-  </si>
-  <si>
-    <t>01/04/2023</t>
+    <t>107521364</t>
+  </si>
+  <si>
+    <t>Nguyễn Văn B</t>
+  </si>
+  <si>
+    <t>NV02</t>
+  </si>
+  <si>
+    <t>Địa chỉ B</t>
   </si>
   <si>
     <t>Cá nhân cư trú</t>
@@ -414,39 +407,24 @@
   </si>
   <si>
     <t>2: Không</t>
-  </si>
-  <si>
-    <t>NV02</t>
-  </si>
-  <si>
-    <t>Địa chỉ B</t>
-  </si>
-  <si>
-    <t>Nguyễn Văn B</t>
-  </si>
-  <si>
-    <t>107521364</t>
-  </si>
-  <si>
-    <t>Tiền lương tiền công</t>
-  </si>
-  <si>
-    <t>TuNgay</t>
-  </si>
-  <si>
-    <t>DenNgay</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -454,50 +432,179 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
-      <color indexed="81"/>
       <name val="Tahoma"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
-      <color indexed="81"/>
       <name val="Tahoma"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="9"/>
-      <color indexed="81"/>
       <name val="Tahoma"/>
       <charset val="1"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -512,18 +619,204 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -531,47 +824,329 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="1" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -620,7 +1195,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -653,26 +1228,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -705,23 +1263,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -863,99 +1404,94 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4ADB66B4-B301-41ED-B48F-710FCDC6CB0D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:R3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="2"/>
   <cols>
-    <col min="2" max="2" width="14.7265625" customWidth="1"/>
+    <col min="2" max="2" width="14.7238095238095" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="12.7265625" customWidth="1"/>
-    <col min="5" max="6" width="19.1796875" customWidth="1"/>
-    <col min="7" max="7" width="15.26953125" customWidth="1"/>
+    <col min="4" max="4" width="12.7238095238095" customWidth="1"/>
+    <col min="5" max="6" width="19.1809523809524" customWidth="1"/>
+    <col min="7" max="7" width="15.2666666666667" customWidth="1"/>
     <col min="8" max="8" width="16" customWidth="1"/>
-    <col min="9" max="9" width="12.81640625" customWidth="1"/>
-    <col min="10" max="10" width="22.1796875" style="7" customWidth="1"/>
-    <col min="11" max="11" width="15.453125" customWidth="1"/>
-    <col min="12" max="13" width="14" style="11" customWidth="1"/>
-    <col min="14" max="14" width="20.1796875" customWidth="1"/>
-    <col min="15" max="15" width="20.81640625" customWidth="1"/>
-    <col min="16" max="16" width="23.26953125" style="4" customWidth="1"/>
-    <col min="17" max="17" width="24.54296875" style="5" customWidth="1"/>
-    <col min="18" max="18" width="19.81640625" customWidth="1"/>
+    <col min="9" max="9" width="12.8190476190476" customWidth="1"/>
+    <col min="10" max="10" width="22.1809523809524" style="2" customWidth="1"/>
+    <col min="11" max="11" width="15.4571428571429" customWidth="1"/>
+    <col min="12" max="13" width="14" style="3" customWidth="1"/>
+    <col min="14" max="14" width="20.1809523809524" customWidth="1"/>
+    <col min="15" max="15" width="20.8190476190476" customWidth="1"/>
+    <col min="16" max="16" width="23.2666666666667" style="4" customWidth="1"/>
+    <col min="17" max="17" width="24.5428571428571" style="5" customWidth="1"/>
+    <col min="18" max="18" width="19.8190476190476" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:18">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="B1" t="s">
+      <c r="F1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="G1" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="6" t="s">
+      <c r="K1" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="N1" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="O1" t="s">
         <v>14</v>
       </c>
-      <c r="L1" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="M1" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="N1" s="3" t="s">
+      <c r="P1" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="O1" t="s">
+      <c r="Q1" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="R1" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="Q1" s="3" t="s">
+    </row>
+    <row r="2" spans="1:18">
+      <c r="A2" t="s">
         <v>18</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="B2" t="s">
         <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>1</v>
       </c>
       <c r="C2" t="s">
         <v>20</v>
@@ -964,34 +1500,34 @@
         <v>21</v>
       </c>
       <c r="E2" t="s">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="F2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I2" t="s">
-        <v>25</v>
-      </c>
-      <c r="J2" s="7">
+        <v>26</v>
+      </c>
+      <c r="J2" s="2">
         <v>1</v>
       </c>
       <c r="K2">
         <v>2023</v>
       </c>
-      <c r="L2" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="M2" s="11" t="s">
+      <c r="L2" s="3" t="s">
         <v>27</v>
       </c>
+      <c r="M2" s="3" t="s">
+        <v>28</v>
+      </c>
       <c r="N2" s="5" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="P2" s="10">
         <v>20000000</v>
@@ -1003,48 +1539,48 @@
         <v>20000000</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A3" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="9" t="s">
+    <row r="3" spans="1:18">
+      <c r="A3" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E3" t="s">
         <v>34</v>
       </c>
-      <c r="C3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D3" t="s">
-        <v>31</v>
-      </c>
-      <c r="E3" t="s">
-        <v>32</v>
-      </c>
       <c r="F3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I3" t="s">
-        <v>25</v>
-      </c>
-      <c r="J3" s="7">
+        <v>26</v>
+      </c>
+      <c r="J3" s="2">
         <v>2</v>
       </c>
       <c r="K3">
         <v>2023</v>
       </c>
-      <c r="L3" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="M3" s="11" t="s">
+      <c r="L3" s="3" t="s">
         <v>27</v>
       </c>
+      <c r="M3" s="3" t="s">
+        <v>28</v>
+      </c>
       <c r="N3" s="5" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="P3" s="10">
         <v>20000000</v>
@@ -1057,40 +1593,42 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6825431-CD75-4952-89A8-789BAD2B1937}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="2" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="32.54296875" customWidth="1"/>
-    <col min="2" max="2" width="25.54296875" customWidth="1"/>
+    <col min="1" max="1" width="32.5428571428571" customWidth="1"/>
+    <col min="2" max="2" width="25.5428571428571" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B1" s="8"/>
+    <row r="1" spans="1:2">
+      <c r="A1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="1"/>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/hddt-SES/src/main/resources/static/cttncn/MauUploadCT_TNCN-TT78.xlsx
+++ b/hddt-SES/src/main/resources/static/cttncn/MauUploadCT_TNCN-TT78.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11730"/>
+    <workbookView windowWidth="28800" windowHeight="12180"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -293,7 +293,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="39">
   <si>
     <t>MaCT(*)</t>
   </si>
@@ -398,6 +398,9 @@
   </si>
   <si>
     <t>Địa chỉ B</t>
+  </si>
+  <si>
+    <t>END</t>
   </si>
   <si>
     <t>Cá nhân cư trú</t>
@@ -419,7 +422,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -429,13 +432,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -585,6 +581,17 @@
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
     </font>
     <font>
       <b/>
@@ -592,19 +599,8 @@
       <name val="Tahoma"/>
       <charset val="134"/>
     </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
-    </font>
   </fonts>
-  <fills count="36">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -691,19 +687,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -925,95 +909,101 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1022,10 +1012,10 @@
     <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1034,10 +1024,10 @@
     <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1046,10 +1036,10 @@
     <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1058,13 +1048,7 @@
     <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1410,8 +1394,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="2"/>
+  <dimension ref="A1:R4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="3"/>
   <cols>
     <col min="2" max="2" width="14.7238095238095" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
@@ -1592,6 +1576,11 @@
         <v>20000000</v>
       </c>
     </row>
+    <row r="4" spans="1:1">
+      <c r="A4" t="s">
+        <v>35</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait"/>
@@ -1612,18 +1601,18 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B1" s="1"/>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/hddt-SES/src/main/resources/static/cttncn/MauUploadCT_TNCN-TT78.xlsx
+++ b/hddt-SES/src/main/resources/static/cttncn/MauUploadCT_TNCN-TT78.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12180"/>
+    <workbookView windowWidth="23040" windowHeight="8940"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,6 +31,7 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>VAN HAU</author>
+    <author>trann</author>
     <author>ASIA</author>
   </authors>
   <commentList>
@@ -117,7 +118,33 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0">
+    <comment ref="F1" authorId="1">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="11"/>
+            <rFont val="Times New Roman"/>
+            <charset val="0"/>
+          </rPr>
+          <t>Số điện thoại liên hệ</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="1">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="11"/>
+            <rFont val="Times New Roman"/>
+            <charset val="0"/>
+          </rPr>
+          <t>Email liên hệ</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -130,7 +157,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0">
+    <comment ref="I1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -143,7 +170,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0">
+    <comment ref="J1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -156,7 +183,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0">
+    <comment ref="K1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -169,7 +196,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="1">
+    <comment ref="L1" authorId="2">
       <text>
         <r>
           <rPr>
@@ -184,7 +211,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="0">
+    <comment ref="M1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -197,7 +224,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L1" authorId="0">
+    <comment ref="N1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -206,11 +233,11 @@
             <rFont val="Tahoma"/>
             <charset val="1"/>
           </rPr>
-          <t>Từ ngày</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="M1" authorId="1">
+          <t>Từ ngày (dd/mm/yyyy)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="O1" authorId="2">
       <text>
         <r>
           <rPr>
@@ -219,11 +246,11 @@
             <rFont val="Tahoma"/>
             <charset val="134"/>
           </rPr>
-          <t>Đến ngày</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="N1" authorId="1">
+          <t>Đến ngày (dd/mm/yyyy)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P1" authorId="2">
       <text>
         <r>
           <rPr>
@@ -236,7 +263,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O1" authorId="0">
+    <comment ref="Q1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -249,7 +276,20 @@
         </r>
       </text>
     </comment>
-    <comment ref="P1" authorId="0">
+    <comment ref="R1" authorId="1">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="11"/>
+            <rFont val="Times New Roman"/>
+            <charset val="0"/>
+          </rPr>
+          <t>Khoản đóng từ thiện, nhân đạo, khuyến học</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="S1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -262,7 +302,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q1" authorId="0">
+    <comment ref="T1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -275,7 +315,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R1" authorId="1">
+    <comment ref="U1" authorId="2">
       <text>
         <r>
           <rPr>
@@ -293,7 +333,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="44">
   <si>
     <t>MaCT(*)</t>
   </si>
@@ -310,6 +350,12 @@
     <t>DiaChiNV</t>
   </si>
   <si>
+    <t>SDTLienHe</t>
+  </si>
+  <si>
+    <t>EmailLienHe</t>
+  </si>
+  <si>
     <t>CMND-CCCD(*)</t>
   </si>
   <si>
@@ -340,6 +386,9 @@
     <t>KhoanDongBHBB</t>
   </si>
   <si>
+    <t>KhoanDongTThienNDaoKHoc</t>
+  </si>
+  <si>
     <t>TongTNChiuThuePhaiKT(*)</t>
   </si>
   <si>
@@ -362,6 +411,12 @@
   </si>
   <si>
     <t>Địa chỉ A</t>
+  </si>
+  <si>
+    <t>0911122233</t>
+  </si>
+  <si>
+    <t>example@gmail.com</t>
   </si>
   <si>
     <t>xxxxxxxxx</t>
@@ -422,7 +477,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -589,15 +644,21 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
-    </font>
-    <font>
       <b/>
       <sz val="9"/>
       <name val="Tahoma"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Times New Roman"/>
+      <charset val="0"/>
     </font>
   </fonts>
   <fills count="34">
@@ -1052,13 +1113,13 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1067,6 +1128,7 @@
     <xf numFmtId="1" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6"/>
     <xf numFmtId="1" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1074,6 +1136,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -1394,27 +1457,31 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R4"/>
+  <dimension ref="A1:U4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="3"/>
   <cols>
     <col min="2" max="2" width="14.7238095238095" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="12.7238095238095" customWidth="1"/>
-    <col min="5" max="6" width="19.1809523809524" customWidth="1"/>
-    <col min="7" max="7" width="15.2666666666667" customWidth="1"/>
-    <col min="8" max="8" width="16" customWidth="1"/>
-    <col min="9" max="9" width="12.8190476190476" customWidth="1"/>
-    <col min="10" max="10" width="22.1809523809524" style="2" customWidth="1"/>
-    <col min="11" max="11" width="15.4571428571429" customWidth="1"/>
-    <col min="12" max="13" width="14" style="3" customWidth="1"/>
-    <col min="14" max="14" width="20.1809523809524" customWidth="1"/>
-    <col min="15" max="15" width="20.8190476190476" customWidth="1"/>
-    <col min="16" max="16" width="23.2666666666667" style="4" customWidth="1"/>
-    <col min="17" max="17" width="24.5428571428571" style="5" customWidth="1"/>
-    <col min="18" max="18" width="19.8190476190476" customWidth="1"/>
+    <col min="5" max="5" width="19.1809523809524" customWidth="1"/>
+    <col min="6" max="6" width="19.1809523809524" style="2" customWidth="1"/>
+    <col min="7" max="7" width="21.5714285714286" style="2" customWidth="1"/>
+    <col min="8" max="8" width="19.1809523809524" customWidth="1"/>
+    <col min="9" max="9" width="15.2666666666667" customWidth="1"/>
+    <col min="10" max="10" width="16" customWidth="1"/>
+    <col min="11" max="11" width="12.8190476190476" customWidth="1"/>
+    <col min="12" max="12" width="22.1809523809524" style="3" customWidth="1"/>
+    <col min="13" max="13" width="15.4571428571429" customWidth="1"/>
+    <col min="14" max="15" width="14" style="2" customWidth="1"/>
+    <col min="16" max="16" width="20.1809523809524" customWidth="1"/>
+    <col min="17" max="17" width="20.8190476190476" customWidth="1"/>
+    <col min="18" max="18" width="29.1428571428571" customWidth="1"/>
+    <col min="19" max="19" width="23.2666666666667" style="4" customWidth="1"/>
+    <col min="20" max="20" width="24.5428571428571" style="5" customWidth="1"/>
+    <col min="21" max="21" width="19.8190476190476" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:21">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -1430,10 +1497,10 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="7" t="s">
@@ -1445,143 +1512,167 @@
       <c r="J1" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="K1" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="9" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="9" t="s">
+      <c r="P1" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="9" t="s">
+      <c r="Q1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="9" t="s">
+      <c r="R1" t="s">
         <v>17</v>
       </c>
+      <c r="S1" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="10" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="2" spans="1:18">
+    <row r="2" spans="1:21">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G2" t="s">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>27</v>
       </c>
       <c r="H2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="I2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K2" t="s">
+        <v>31</v>
+      </c>
+      <c r="L2" s="3">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>2023</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P2" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="S2" s="11">
+        <v>20000000</v>
+      </c>
+      <c r="T2" s="11">
+        <v>20000000</v>
+      </c>
+      <c r="U2" s="11">
+        <v>20000000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21">
+      <c r="A3" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F3" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="J2" s="2">
-        <v>1</v>
-      </c>
-      <c r="K2">
+      <c r="G3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J3" t="s">
+        <v>30</v>
+      </c>
+      <c r="K3" t="s">
+        <v>31</v>
+      </c>
+      <c r="L3" s="3">
+        <v>2</v>
+      </c>
+      <c r="M3">
         <v>2023</v>
       </c>
-      <c r="L2" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="N2" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="P2" s="10">
+      <c r="N3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P3" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="S3" s="11">
         <v>20000000</v>
       </c>
-      <c r="Q2" s="10">
+      <c r="T3" s="11">
         <v>20000000</v>
       </c>
-      <c r="R2" s="10">
-        <v>20000000</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18">
-      <c r="A3" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="C3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H3" t="s">
-        <v>25</v>
-      </c>
-      <c r="I3" t="s">
-        <v>26</v>
-      </c>
-      <c r="J3" s="2">
-        <v>2</v>
-      </c>
-      <c r="K3">
-        <v>2023</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="N3" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="P3" s="10">
-        <v>20000000</v>
-      </c>
-      <c r="Q3" s="10">
-        <v>20000000</v>
-      </c>
-      <c r="R3" s="10">
+      <c r="U3" s="11">
         <v>20000000</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="G2" r:id="rId3" display="example@gmail.com"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait"/>
   <headerFooter/>
@@ -1601,18 +1692,18 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B1" s="1"/>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/hddt-SES/src/main/resources/static/cttncn/MauUploadCT_TNCN-TT78.xlsx
+++ b/hddt-SES/src/main/resources/static/cttncn/MauUploadCT_TNCN-TT78.xlsx
@@ -144,7 +144,20 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0">
+    <comment ref="H1" authorId="1">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="11"/>
+            <rFont val="Times New Roman"/>
+            <charset val="0"/>
+          </rPr>
+          <t>Cách nhau bởi dấu ,</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -157,7 +170,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0">
+    <comment ref="J1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -170,7 +183,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="0">
+    <comment ref="K1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -183,7 +196,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="0">
+    <comment ref="L1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -196,7 +209,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L1" authorId="2">
+    <comment ref="M1" authorId="2">
       <text>
         <r>
           <rPr>
@@ -211,7 +224,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M1" authorId="0">
+    <comment ref="N1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -224,7 +237,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N1" authorId="0">
+    <comment ref="O1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -237,7 +250,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O1" authorId="2">
+    <comment ref="P1" authorId="2">
       <text>
         <r>
           <rPr>
@@ -250,7 +263,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P1" authorId="2">
+    <comment ref="Q1" authorId="2">
       <text>
         <r>
           <rPr>
@@ -263,7 +276,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q1" authorId="0">
+    <comment ref="R1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -276,7 +289,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R1" authorId="1">
+    <comment ref="S1" authorId="1">
       <text>
         <r>
           <rPr>
@@ -289,7 +302,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S1" authorId="0">
+    <comment ref="T1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -302,7 +315,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T1" authorId="0">
+    <comment ref="U1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -315,7 +328,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U1" authorId="2">
+    <comment ref="V1" authorId="2">
       <text>
         <r>
           <rPr>
@@ -333,7 +346,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="45">
   <si>
     <t>MaCT(*)</t>
   </si>
@@ -354,6 +367,9 @@
   </si>
   <si>
     <t>EmailLienHe</t>
+  </si>
+  <si>
+    <t>EmailCC</t>
   </si>
   <si>
     <t>CMND-CCCD(*)</t>
@@ -638,6 +654,11 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
       <name val="Tahoma"/>
@@ -645,20 +666,15 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <name val="Times New Roman"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <b/>
       <sz val="9"/>
       <name val="Tahoma"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Times New Roman"/>
-      <charset val="0"/>
     </font>
   </fonts>
   <fills count="34">
@@ -1128,7 +1144,7 @@
     <xf numFmtId="1" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
     <xf numFmtId="1" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1457,7 +1473,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:U4"/>
+  <dimension ref="A1:V4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="3"/>
   <cols>
     <col min="2" max="2" width="14.7238095238095" customWidth="1"/>
@@ -1465,23 +1481,23 @@
     <col min="4" max="4" width="12.7238095238095" customWidth="1"/>
     <col min="5" max="5" width="19.1809523809524" customWidth="1"/>
     <col min="6" max="6" width="19.1809523809524" style="2" customWidth="1"/>
-    <col min="7" max="7" width="21.5714285714286" style="2" customWidth="1"/>
-    <col min="8" max="8" width="19.1809523809524" customWidth="1"/>
-    <col min="9" max="9" width="15.2666666666667" customWidth="1"/>
-    <col min="10" max="10" width="16" customWidth="1"/>
-    <col min="11" max="11" width="12.8190476190476" customWidth="1"/>
-    <col min="12" max="12" width="22.1809523809524" style="3" customWidth="1"/>
-    <col min="13" max="13" width="15.4571428571429" customWidth="1"/>
-    <col min="14" max="15" width="14" style="2" customWidth="1"/>
-    <col min="16" max="16" width="20.1809523809524" customWidth="1"/>
-    <col min="17" max="17" width="20.8190476190476" customWidth="1"/>
-    <col min="18" max="18" width="29.1428571428571" customWidth="1"/>
-    <col min="19" max="19" width="23.2666666666667" style="4" customWidth="1"/>
-    <col min="20" max="20" width="24.5428571428571" style="5" customWidth="1"/>
-    <col min="21" max="21" width="19.8190476190476" customWidth="1"/>
+    <col min="7" max="8" width="21.5714285714286" style="2" customWidth="1"/>
+    <col min="9" max="9" width="19.1809523809524" customWidth="1"/>
+    <col min="10" max="10" width="15.2666666666667" customWidth="1"/>
+    <col min="11" max="11" width="16" customWidth="1"/>
+    <col min="12" max="12" width="12.8190476190476" customWidth="1"/>
+    <col min="13" max="13" width="22.1809523809524" style="3" customWidth="1"/>
+    <col min="14" max="14" width="15.4571428571429" customWidth="1"/>
+    <col min="15" max="16" width="14" style="2" customWidth="1"/>
+    <col min="17" max="17" width="20.1809523809524" customWidth="1"/>
+    <col min="18" max="18" width="20.8190476190476" customWidth="1"/>
+    <col min="19" max="19" width="29.1428571428571" customWidth="1"/>
+    <col min="20" max="20" width="23.2666666666667" style="4" customWidth="1"/>
+    <col min="21" max="21" width="24.5428571428571" style="5" customWidth="1"/>
+    <col min="22" max="22" width="19.8190476190476" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21">
+    <row r="1" spans="1:22">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -1503,7 +1519,7 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="7" t="s">
@@ -1518,25 +1534,25 @@
       <c r="L1" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="M1" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="9" t="s">
         <v>13</v>
       </c>
       <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="10" t="s">
+      <c r="P1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="Q1" s="10" t="s">
         <v>16</v>
       </c>
       <c r="R1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="10" t="s">
+      <c r="S1" t="s">
         <v>18</v>
       </c>
       <c r="T1" s="10" t="s">
@@ -1545,32 +1561,33 @@
       <c r="U1" s="10" t="s">
         <v>20</v>
       </c>
+      <c r="V1" s="10" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="2" spans="1:21">
+    <row r="2" spans="1:22">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="H2" t="s">
         <v>28</v>
       </c>
+      <c r="H2" s="8"/>
       <c r="I2" t="s">
         <v>29</v>
       </c>
@@ -1580,23 +1597,23 @@
       <c r="K2" t="s">
         <v>31</v>
       </c>
-      <c r="L2" s="3">
+      <c r="L2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M2" s="3">
         <v>1</v>
       </c>
-      <c r="M2">
+      <c r="N2">
         <v>2023</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>32</v>
       </c>
       <c r="O2" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="P2" s="5" t="s">
+      <c r="P2" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="S2" s="11">
-        <v>20000000</v>
+      <c r="Q2" s="5" t="s">
+        <v>35</v>
       </c>
       <c r="T2" s="11">
         <v>20000000</v>
@@ -1604,32 +1621,33 @@
       <c r="U2" s="11">
         <v>20000000</v>
       </c>
+      <c r="V2" s="11">
+        <v>20000000</v>
+      </c>
     </row>
-    <row r="3" spans="1:21">
+    <row r="3" spans="1:22">
       <c r="A3" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H3" t="s">
         <v>28</v>
       </c>
+      <c r="H3"/>
       <c r="I3" t="s">
         <v>29</v>
       </c>
@@ -1639,34 +1657,37 @@
       <c r="K3" t="s">
         <v>31</v>
       </c>
-      <c r="L3" s="3">
+      <c r="L3" t="s">
+        <v>32</v>
+      </c>
+      <c r="M3" s="3">
         <v>2</v>
       </c>
-      <c r="M3">
+      <c r="N3">
         <v>2023</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>32</v>
       </c>
       <c r="O3" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="P3" s="5" t="s">
+      <c r="P3" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="S3" s="11">
-        <v>20000000</v>
+      <c r="Q3" s="5" t="s">
+        <v>35</v>
       </c>
       <c r="T3" s="11">
         <v>20000000</v>
       </c>
       <c r="U3" s="11">
+        <v>20000000</v>
+      </c>
+      <c r="V3" s="11">
         <v>20000000</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -1692,18 +1713,18 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B1" s="1"/>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
